--- a/data.xlsx
+++ b/data.xlsx
@@ -2,9 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="World Cup Dummy Data" sheetId="1" r:id="Red8085d729494d96"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="Red9f032c1c624a73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theme Counts" sheetId="3" r:id="R127c6117932b4587"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="World Cup Dummy Data" sheetId="1" r:id="R126acca244b44f09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="R323d9b004979405f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theme Counts" sheetId="3" r:id="R78d321a9f8e340f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venn Zone Counts" sheetId="4" r:id="Rb919ff03bdfd47fa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -27,7 +28,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -39,15 +40,62 @@
         <x:fgColor rgb="FF1F4E78"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F2937"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="11">
     <x:border/>
     <x:border/>
+    <x:border>
+      <x:right/>
+      <x:bottom/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:bottom/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:bottom/>
+    </x:border>
+    <x:border>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:top/>
+      <x:bottom/>
+    </x:border>
+    <x:border>
+      <x:right/>
+      <x:top/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:top/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -84,6 +132,21 @@
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -324,7 +387,7 @@
         <x:v>Building a balanced squad with the right mix of quality, roles, depth and tournament readiness.</x:v>
       </x:c>
       <x:c r="D2" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>UTS</x:v>
       </x:c>
       <x:c r="E2" s="12" t="str">
         <x:v>Build a tournament-ready squad</x:v>
@@ -402,7 +465,7 @@
         <x:v>Building a balanced squad with the right mix of quality, roles, depth and tournament readiness.</x:v>
       </x:c>
       <x:c r="D5" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>UTS</x:v>
       </x:c>
       <x:c r="E5" s="12" t="str">
         <x:v>Build a tournament-ready squad</x:v>
@@ -428,7 +491,7 @@
         <x:v>Building a balanced squad with the right mix of quality, roles, depth and tournament readiness.</x:v>
       </x:c>
       <x:c r="D6" s="12" t="str">
-        <x:v>FDS</x:v>
+        <x:v>UTS</x:v>
       </x:c>
       <x:c r="E6" s="12" t="str">
         <x:v>Build a tournament-ready squad</x:v>
@@ -454,7 +517,7 @@
         <x:v>Building a balanced squad with the right mix of quality, roles, depth and tournament readiness.</x:v>
       </x:c>
       <x:c r="D7" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>UTS</x:v>
       </x:c>
       <x:c r="E7" s="12" t="str">
         <x:v>Build a tournament-ready squad</x:v>
@@ -480,7 +543,7 @@
         <x:v>Building a balanced squad with the right mix of quality, roles, depth and tournament readiness.</x:v>
       </x:c>
       <x:c r="D8" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>UTS</x:v>
       </x:c>
       <x:c r="E8" s="12" t="str">
         <x:v>Build a tournament-ready squad</x:v>
@@ -506,7 +569,7 @@
         <x:v>Building a balanced squad with the right mix of quality, roles, depth and tournament readiness.</x:v>
       </x:c>
       <x:c r="D9" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>UTS</x:v>
       </x:c>
       <x:c r="E9" s="12" t="str">
         <x:v>Build a tournament-ready squad</x:v>
@@ -532,7 +595,7 @@
         <x:v>Building a balanced squad with the right mix of quality, roles, depth and tournament readiness.</x:v>
       </x:c>
       <x:c r="D10" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>UTS</x:v>
       </x:c>
       <x:c r="E10" s="12" t="str">
         <x:v>Build a tournament-ready squad</x:v>
@@ -584,7 +647,7 @@
         <x:v>Building a balanced squad with the right mix of quality, roles, depth and tournament readiness.</x:v>
       </x:c>
       <x:c r="D12" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>UTS</x:v>
       </x:c>
       <x:c r="E12" s="12" t="str">
         <x:v>Build a tournament-ready squad</x:v>
@@ -610,7 +673,7 @@
         <x:v>Building a balanced squad with the right mix of quality, roles, depth and tournament readiness.</x:v>
       </x:c>
       <x:c r="D13" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>UTS</x:v>
       </x:c>
       <x:c r="E13" s="12" t="str">
         <x:v>Build a tournament-ready squad</x:v>
@@ -636,7 +699,7 @@
         <x:v>Building a balanced squad with the right mix of quality, roles, depth and tournament readiness.</x:v>
       </x:c>
       <x:c r="D14" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>UTS</x:v>
       </x:c>
       <x:c r="E14" s="12" t="str">
         <x:v>Build a tournament-ready squad</x:v>
@@ -688,7 +751,7 @@
         <x:v>Building a balanced squad with the right mix of quality, roles, depth and tournament readiness.</x:v>
       </x:c>
       <x:c r="D16" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>UTS</x:v>
       </x:c>
       <x:c r="E16" s="12" t="str">
         <x:v>Build a tournament-ready squad</x:v>
@@ -714,7 +777,7 @@
         <x:v>Building a balanced squad with the right mix of quality, roles, depth and tournament readiness.</x:v>
       </x:c>
       <x:c r="D17" s="12" t="str">
-        <x:v>UTS + CI</x:v>
+        <x:v>UTS</x:v>
       </x:c>
       <x:c r="E17" s="12" t="str">
         <x:v>Build a tournament-ready squad</x:v>
@@ -818,7 +881,7 @@
         <x:v>Building a balanced squad with the right mix of quality, roles, depth and tournament readiness.</x:v>
       </x:c>
       <x:c r="D21" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>UTS</x:v>
       </x:c>
       <x:c r="E21" s="12" t="str">
         <x:v>Build a tournament-ready squad</x:v>
@@ -844,7 +907,7 @@
         <x:v>Building a balanced squad with the right mix of quality, roles, depth and tournament readiness.</x:v>
       </x:c>
       <x:c r="D22" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>UTS</x:v>
       </x:c>
       <x:c r="E22" s="12" t="str">
         <x:v>Build a tournament-ready squad</x:v>
@@ -870,7 +933,7 @@
         <x:v>Building a balanced squad with the right mix of quality, roles, depth and tournament readiness.</x:v>
       </x:c>
       <x:c r="D23" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>UTS</x:v>
       </x:c>
       <x:c r="E23" s="12" t="str">
         <x:v>Build a tournament-ready squad</x:v>
@@ -896,7 +959,7 @@
         <x:v>Building a balanced squad with the right mix of quality, roles, depth and tournament readiness.</x:v>
       </x:c>
       <x:c r="D24" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>UTS</x:v>
       </x:c>
       <x:c r="E24" s="12" t="str">
         <x:v>Build a tournament-ready squad</x:v>
@@ -948,7 +1011,7 @@
         <x:v>Building a balanced squad with the right mix of quality, roles, depth and tournament readiness.</x:v>
       </x:c>
       <x:c r="D26" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>UTS</x:v>
       </x:c>
       <x:c r="E26" s="12" t="str">
         <x:v>Build a tournament-ready squad</x:v>
@@ -974,7 +1037,7 @@
         <x:v>Building a balanced squad with the right mix of quality, roles, depth and tournament readiness.</x:v>
       </x:c>
       <x:c r="D27" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>UTS</x:v>
       </x:c>
       <x:c r="E27" s="12" t="str">
         <x:v>Build a tournament-ready squad</x:v>
@@ -1000,7 +1063,7 @@
         <x:v>Building a balanced squad with the right mix of quality, roles, depth and tournament readiness.</x:v>
       </x:c>
       <x:c r="D28" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>UTS</x:v>
       </x:c>
       <x:c r="E28" s="12" t="str">
         <x:v>Build a tournament-ready squad</x:v>
@@ -1026,7 +1089,7 @@
         <x:v>Building a balanced squad with the right mix of quality, roles, depth and tournament readiness.</x:v>
       </x:c>
       <x:c r="D29" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>UTS</x:v>
       </x:c>
       <x:c r="E29" s="12" t="str">
         <x:v>Build a tournament-ready squad</x:v>
@@ -1052,7 +1115,7 @@
         <x:v>Building a balanced squad with the right mix of quality, roles, depth and tournament readiness.</x:v>
       </x:c>
       <x:c r="D30" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>UTS</x:v>
       </x:c>
       <x:c r="E30" s="12" t="str">
         <x:v>Build a tournament-ready squad</x:v>
@@ -1078,7 +1141,7 @@
         <x:v>Building a balanced squad with the right mix of quality, roles, depth and tournament readiness.</x:v>
       </x:c>
       <x:c r="D31" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>UTS</x:v>
       </x:c>
       <x:c r="E31" s="12" t="str">
         <x:v>Build a tournament-ready squad</x:v>
@@ -1104,7 +1167,7 @@
         <x:v>Building a balanced squad with the right mix of quality, roles, depth and tournament readiness.</x:v>
       </x:c>
       <x:c r="D32" s="12" t="str">
-        <x:v>UTS + CI</x:v>
+        <x:v>UTS</x:v>
       </x:c>
       <x:c r="E32" s="12" t="str">
         <x:v>Build a tournament-ready squad</x:v>
@@ -1130,7 +1193,7 @@
         <x:v>Building a balanced squad with the right mix of quality, roles, depth and tournament readiness.</x:v>
       </x:c>
       <x:c r="D33" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>UTS</x:v>
       </x:c>
       <x:c r="E33" s="12" t="str">
         <x:v>Build a tournament-ready squad</x:v>
@@ -1156,7 +1219,7 @@
         <x:v>Building a balanced squad with the right mix of quality, roles, depth and tournament readiness.</x:v>
       </x:c>
       <x:c r="D34" s="12" t="str">
-        <x:v>UTS + CI</x:v>
+        <x:v>UTS</x:v>
       </x:c>
       <x:c r="E34" s="12" t="str">
         <x:v>Build a tournament-ready squad</x:v>
@@ -1182,7 +1245,7 @@
         <x:v>Building a balanced squad with the right mix of quality, roles, depth and tournament readiness.</x:v>
       </x:c>
       <x:c r="D35" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>UTS</x:v>
       </x:c>
       <x:c r="E35" s="12" t="str">
         <x:v>Build a tournament-ready squad</x:v>
@@ -1208,7 +1271,7 @@
         <x:v>Building a balanced squad with the right mix of quality, roles, depth and tournament readiness.</x:v>
       </x:c>
       <x:c r="D36" s="12" t="str">
-        <x:v>FDS</x:v>
+        <x:v>UTS</x:v>
       </x:c>
       <x:c r="E36" s="12" t="str">
         <x:v>Build a tournament-ready squad</x:v>
@@ -1234,7 +1297,7 @@
         <x:v>Building a balanced squad with the right mix of quality, roles, depth and tournament readiness.</x:v>
       </x:c>
       <x:c r="D37" s="12" t="str">
-        <x:v>UTS + CI + FDS</x:v>
+        <x:v>UTS</x:v>
       </x:c>
       <x:c r="E37" s="12" t="str">
         <x:v>Build a tournament-ready squad</x:v>
@@ -1260,7 +1323,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D38" s="12" t="str">
-        <x:v>UTS + CI + FDS</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E38" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -1286,7 +1349,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D39" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E39" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -1312,7 +1375,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D40" s="12" t="str">
-        <x:v>UTS + CI + FDS</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E40" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -1338,7 +1401,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D41" s="12" t="str">
-        <x:v>UTS + CI + FDS</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E41" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -1390,7 +1453,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D43" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E43" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -1416,7 +1479,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D44" s="12" t="str">
-        <x:v>UTS + CI</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E44" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -1442,7 +1505,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D45" s="12" t="str">
-        <x:v>FDS</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E45" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -1468,7 +1531,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D46" s="12" t="str">
-        <x:v>FDS</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E46" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -1546,7 +1609,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D49" s="12" t="str">
-        <x:v>UTS + CI + FDS</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E49" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -1572,7 +1635,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D50" s="12" t="str">
-        <x:v>FDS</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E50" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -1598,7 +1661,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D51" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E51" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -1624,7 +1687,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D52" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E52" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -1650,7 +1713,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D53" s="12" t="str">
-        <x:v>UTS + CI</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E53" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -1676,7 +1739,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D54" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E54" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -1702,7 +1765,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D55" s="12" t="str">
-        <x:v>FDS</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E55" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -1728,7 +1791,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D56" s="12" t="str">
-        <x:v>UTS + CI + FDS</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E56" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -1754,7 +1817,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D57" s="12" t="str">
-        <x:v>FDS</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E57" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -1780,7 +1843,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D58" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E58" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -1806,7 +1869,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D59" s="12" t="str">
-        <x:v>FDS</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E59" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -1832,7 +1895,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D60" s="12" t="str">
-        <x:v>UTS + CI + FDS</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E60" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -1858,7 +1921,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D61" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E61" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -1884,7 +1947,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D62" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E62" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -1910,7 +1973,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D63" s="12" t="str">
-        <x:v>UTS + CI</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E63" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -1936,7 +1999,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D64" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E64" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -1962,7 +2025,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D65" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E65" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -1988,7 +2051,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D66" s="12" t="str">
-        <x:v>UTS + CI</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E66" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -2014,7 +2077,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D67" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E67" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -2040,7 +2103,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D68" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E68" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -2066,7 +2129,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D69" s="12" t="str">
-        <x:v>FDS</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E69" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -2092,7 +2155,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D70" s="12" t="str">
-        <x:v>UTS + CI + FDS</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E70" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -2118,7 +2181,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D71" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E71" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -2144,7 +2207,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D72" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E72" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -2170,7 +2233,7 @@
         <x:v>Creating a clear way of playing that can adapt to different opponents and match situations.</x:v>
       </x:c>
       <x:c r="D73" s="12" t="str">
-        <x:v>UTS + CI + FDS</x:v>
+        <x:v>CI</x:v>
       </x:c>
       <x:c r="E73" s="12" t="str">
         <x:v>Create a flexible winning game model</x:v>
@@ -2222,7 +2285,7 @@
         <x:v>Managing player conditioning, recovery and rotation across a demanding tournament schedule.</x:v>
       </x:c>
       <x:c r="D75" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E75" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -2248,7 +2311,7 @@
         <x:v>Managing player conditioning, recovery and rotation across a demanding tournament schedule.</x:v>
       </x:c>
       <x:c r="D76" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E76" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -2274,7 +2337,7 @@
         <x:v>Managing player conditioning, recovery and rotation across a demanding tournament schedule.</x:v>
       </x:c>
       <x:c r="D77" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E77" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -2300,7 +2363,7 @@
         <x:v>Managing player conditioning, recovery and rotation across a demanding tournament schedule.</x:v>
       </x:c>
       <x:c r="D78" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E78" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -2326,7 +2389,7 @@
         <x:v>Managing player conditioning, recovery and rotation across a demanding tournament schedule.</x:v>
       </x:c>
       <x:c r="D79" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E79" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -2352,7 +2415,7 @@
         <x:v>Managing player conditioning, recovery and rotation across a demanding tournament schedule.</x:v>
       </x:c>
       <x:c r="D80" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E80" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -2378,7 +2441,7 @@
         <x:v>Managing player conditioning, recovery and rotation across a demanding tournament schedule.</x:v>
       </x:c>
       <x:c r="D81" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E81" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -2404,7 +2467,7 @@
         <x:v>Managing player conditioning, recovery and rotation across a demanding tournament schedule.</x:v>
       </x:c>
       <x:c r="D82" s="12" t="str">
-        <x:v>UTS + CI + FDS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E82" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -2456,7 +2519,7 @@
         <x:v>Managing player conditioning, recovery and rotation across a demanding tournament schedule.</x:v>
       </x:c>
       <x:c r="D84" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E84" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -2482,7 +2545,7 @@
         <x:v>Managing player conditioning, recovery and rotation across a demanding tournament schedule.</x:v>
       </x:c>
       <x:c r="D85" s="12" t="str">
-        <x:v>UTS + CI + FDS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E85" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -2508,7 +2571,7 @@
         <x:v>Managing player conditioning, recovery and rotation across a demanding tournament schedule.</x:v>
       </x:c>
       <x:c r="D86" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E86" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -2534,7 +2597,7 @@
         <x:v>Managing player conditioning, recovery and rotation across a demanding tournament schedule.</x:v>
       </x:c>
       <x:c r="D87" s="12" t="str">
-        <x:v>UTS + CI + FDS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E87" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -2560,7 +2623,7 @@
         <x:v>Managing player conditioning, recovery and rotation across a demanding tournament schedule.</x:v>
       </x:c>
       <x:c r="D88" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E88" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -2586,7 +2649,7 @@
         <x:v>Managing player conditioning, recovery and rotation across a demanding tournament schedule.</x:v>
       </x:c>
       <x:c r="D89" s="12" t="str">
-        <x:v>UTS + CI</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E89" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -2638,7 +2701,7 @@
         <x:v>Managing player conditioning, recovery and rotation across a demanding tournament schedule.</x:v>
       </x:c>
       <x:c r="D91" s="12" t="str">
-        <x:v>UTS + CI</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E91" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -2664,7 +2727,7 @@
         <x:v>Managing player conditioning, recovery and rotation across a demanding tournament schedule.</x:v>
       </x:c>
       <x:c r="D92" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E92" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -2690,7 +2753,7 @@
         <x:v>Managing player conditioning, recovery and rotation across a demanding tournament schedule.</x:v>
       </x:c>
       <x:c r="D93" s="12" t="str">
-        <x:v>UTS + CI + FDS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E93" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -2742,7 +2805,7 @@
         <x:v>Managing player conditioning, recovery and rotation across a demanding tournament schedule.</x:v>
       </x:c>
       <x:c r="D95" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E95" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -2820,7 +2883,7 @@
         <x:v>Managing player conditioning, recovery and rotation across a demanding tournament schedule.</x:v>
       </x:c>
       <x:c r="D98" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E98" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -2846,7 +2909,7 @@
         <x:v>Managing player conditioning, recovery and rotation across a demanding tournament schedule.</x:v>
       </x:c>
       <x:c r="D99" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E99" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -2898,7 +2961,7 @@
         <x:v>Managing player conditioning, recovery and rotation across a demanding tournament schedule.</x:v>
       </x:c>
       <x:c r="D101" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E101" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -2924,7 +2987,7 @@
         <x:v>Managing player conditioning, recovery and rotation across a demanding tournament schedule.</x:v>
       </x:c>
       <x:c r="D102" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E102" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -2950,7 +3013,7 @@
         <x:v>Managing player conditioning, recovery and rotation across a demanding tournament schedule.</x:v>
       </x:c>
       <x:c r="D103" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E103" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -2976,7 +3039,7 @@
         <x:v>Managing player conditioning, recovery and rotation across a demanding tournament schedule.</x:v>
       </x:c>
       <x:c r="D104" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E104" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -3002,7 +3065,7 @@
         <x:v>Managing player conditioning, recovery and rotation across a demanding tournament schedule.</x:v>
       </x:c>
       <x:c r="D105" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E105" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -3028,7 +3091,7 @@
         <x:v>Managing player conditioning, recovery and rotation across a demanding tournament schedule.</x:v>
       </x:c>
       <x:c r="D106" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E106" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -3054,7 +3117,7 @@
         <x:v>Managing player conditioning, recovery and rotation across a demanding tournament schedule.</x:v>
       </x:c>
       <x:c r="D107" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E107" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -3080,7 +3143,7 @@
         <x:v>Managing player conditioning, recovery and rotation across a demanding tournament schedule.</x:v>
       </x:c>
       <x:c r="D108" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E108" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -3106,7 +3169,7 @@
         <x:v>Managing player conditioning, recovery and rotation across a demanding tournament schedule.</x:v>
       </x:c>
       <x:c r="D109" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E109" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -3132,7 +3195,7 @@
         <x:v>Developing the belief, leadership and unity needed to perform under pressure.</x:v>
       </x:c>
       <x:c r="D110" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>UTS + CI</x:v>
       </x:c>
       <x:c r="E110" s="12" t="str">
         <x:v>Build a resilient and united team culture</x:v>
@@ -3158,7 +3221,7 @@
         <x:v>Developing the belief, leadership and unity needed to perform under pressure.</x:v>
       </x:c>
       <x:c r="D111" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>UTS + CI</x:v>
       </x:c>
       <x:c r="E111" s="12" t="str">
         <x:v>Build a resilient and united team culture</x:v>
@@ -3236,7 +3299,7 @@
         <x:v>Developing the belief, leadership and unity needed to perform under pressure.</x:v>
       </x:c>
       <x:c r="D114" s="12" t="str">
-        <x:v>FDS</x:v>
+        <x:v>UTS + CI</x:v>
       </x:c>
       <x:c r="E114" s="12" t="str">
         <x:v>Build a resilient and united team culture</x:v>
@@ -3262,7 +3325,7 @@
         <x:v>Developing the belief, leadership and unity needed to perform under pressure.</x:v>
       </x:c>
       <x:c r="D115" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>UTS + CI</x:v>
       </x:c>
       <x:c r="E115" s="12" t="str">
         <x:v>Build a resilient and united team culture</x:v>
@@ -3288,7 +3351,7 @@
         <x:v>Developing the belief, leadership and unity needed to perform under pressure.</x:v>
       </x:c>
       <x:c r="D116" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>UTS + CI</x:v>
       </x:c>
       <x:c r="E116" s="12" t="str">
         <x:v>Build a resilient and united team culture</x:v>
@@ -3314,7 +3377,7 @@
         <x:v>Developing the belief, leadership and unity needed to perform under pressure.</x:v>
       </x:c>
       <x:c r="D117" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>UTS + CI</x:v>
       </x:c>
       <x:c r="E117" s="12" t="str">
         <x:v>Build a resilient and united team culture</x:v>
@@ -3340,7 +3403,7 @@
         <x:v>Developing the belief, leadership and unity needed to perform under pressure.</x:v>
       </x:c>
       <x:c r="D118" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>UTS + CI</x:v>
       </x:c>
       <x:c r="E118" s="12" t="str">
         <x:v>Build a resilient and united team culture</x:v>
@@ -3366,7 +3429,7 @@
         <x:v>Developing the belief, leadership and unity needed to perform under pressure.</x:v>
       </x:c>
       <x:c r="D119" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>UTS + CI</x:v>
       </x:c>
       <x:c r="E119" s="12" t="str">
         <x:v>Build a resilient and united team culture</x:v>
@@ -3392,7 +3455,7 @@
         <x:v>Developing the belief, leadership and unity needed to perform under pressure.</x:v>
       </x:c>
       <x:c r="D120" s="12" t="str">
-        <x:v>FDS</x:v>
+        <x:v>UTS + CI</x:v>
       </x:c>
       <x:c r="E120" s="12" t="str">
         <x:v>Build a resilient and united team culture</x:v>
@@ -3418,7 +3481,7 @@
         <x:v>Developing the belief, leadership and unity needed to perform under pressure.</x:v>
       </x:c>
       <x:c r="D121" s="12" t="str">
-        <x:v>UTS + CI + FDS</x:v>
+        <x:v>UTS + CI</x:v>
       </x:c>
       <x:c r="E121" s="12" t="str">
         <x:v>Build a resilient and united team culture</x:v>
@@ -3444,7 +3507,7 @@
         <x:v>Developing the belief, leadership and unity needed to perform under pressure.</x:v>
       </x:c>
       <x:c r="D122" s="12" t="str">
-        <x:v>UTS + CI + FDS</x:v>
+        <x:v>UTS + CI</x:v>
       </x:c>
       <x:c r="E122" s="12" t="str">
         <x:v>Build a resilient and united team culture</x:v>
@@ -3470,7 +3533,7 @@
         <x:v>Developing the belief, leadership and unity needed to perform under pressure.</x:v>
       </x:c>
       <x:c r="D123" s="12" t="str">
-        <x:v>UTS + CI + FDS</x:v>
+        <x:v>UTS + CI</x:v>
       </x:c>
       <x:c r="E123" s="12" t="str">
         <x:v>Build a resilient and united team culture</x:v>
@@ -3496,7 +3559,7 @@
         <x:v>Developing the belief, leadership and unity needed to perform under pressure.</x:v>
       </x:c>
       <x:c r="D124" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>UTS + CI</x:v>
       </x:c>
       <x:c r="E124" s="12" t="str">
         <x:v>Build a resilient and united team culture</x:v>
@@ -3522,7 +3585,7 @@
         <x:v>Developing the belief, leadership and unity needed to perform under pressure.</x:v>
       </x:c>
       <x:c r="D125" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>UTS + CI</x:v>
       </x:c>
       <x:c r="E125" s="12" t="str">
         <x:v>Build a resilient and united team culture</x:v>
@@ -3548,7 +3611,7 @@
         <x:v>Developing the belief, leadership and unity needed to perform under pressure.</x:v>
       </x:c>
       <x:c r="D126" s="12" t="str">
-        <x:v>UTS + CI + FDS</x:v>
+        <x:v>UTS + CI</x:v>
       </x:c>
       <x:c r="E126" s="12" t="str">
         <x:v>Build a resilient and united team culture</x:v>
@@ -3574,7 +3637,7 @@
         <x:v>Developing the belief, leadership and unity needed to perform under pressure.</x:v>
       </x:c>
       <x:c r="D127" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>UTS + CI</x:v>
       </x:c>
       <x:c r="E127" s="12" t="str">
         <x:v>Build a resilient and united team culture</x:v>
@@ -3600,7 +3663,7 @@
         <x:v>Developing the belief, leadership and unity needed to perform under pressure.</x:v>
       </x:c>
       <x:c r="D128" s="12" t="str">
-        <x:v>UTS + CI + FDS</x:v>
+        <x:v>UTS + CI</x:v>
       </x:c>
       <x:c r="E128" s="12" t="str">
         <x:v>Build a resilient and united team culture</x:v>
@@ -3626,7 +3689,7 @@
         <x:v>Developing the belief, leadership and unity needed to perform under pressure.</x:v>
       </x:c>
       <x:c r="D129" s="12" t="str">
-        <x:v>FDS</x:v>
+        <x:v>UTS + CI</x:v>
       </x:c>
       <x:c r="E129" s="12" t="str">
         <x:v>Build a resilient and united team culture</x:v>
@@ -3678,7 +3741,7 @@
         <x:v>Developing the belief, leadership and unity needed to perform under pressure.</x:v>
       </x:c>
       <x:c r="D131" s="12" t="str">
-        <x:v>FDS</x:v>
+        <x:v>UTS + CI</x:v>
       </x:c>
       <x:c r="E131" s="12" t="str">
         <x:v>Build a resilient and united team culture</x:v>
@@ -3704,7 +3767,7 @@
         <x:v>Developing the belief, leadership and unity needed to perform under pressure.</x:v>
       </x:c>
       <x:c r="D132" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>UTS + CI</x:v>
       </x:c>
       <x:c r="E132" s="12" t="str">
         <x:v>Build a resilient and united team culture</x:v>
@@ -3730,7 +3793,7 @@
         <x:v>Developing the belief, leadership and unity needed to perform under pressure.</x:v>
       </x:c>
       <x:c r="D133" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>UTS + CI</x:v>
       </x:c>
       <x:c r="E133" s="12" t="str">
         <x:v>Build a resilient and united team culture</x:v>
@@ -3756,7 +3819,7 @@
         <x:v>Developing the belief, leadership and unity needed to perform under pressure.</x:v>
       </x:c>
       <x:c r="D134" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>UTS + CI</x:v>
       </x:c>
       <x:c r="E134" s="12" t="str">
         <x:v>Build a resilient and united team culture</x:v>
@@ -3782,7 +3845,7 @@
         <x:v>Developing the belief, leadership and unity needed to perform under pressure.</x:v>
       </x:c>
       <x:c r="D135" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>UTS + CI</x:v>
       </x:c>
       <x:c r="E135" s="12" t="str">
         <x:v>Build a resilient and united team culture</x:v>
@@ -3808,7 +3871,7 @@
         <x:v>Developing the belief, leadership and unity needed to perform under pressure.</x:v>
       </x:c>
       <x:c r="D136" s="12" t="str">
-        <x:v>FDS</x:v>
+        <x:v>UTS + CI</x:v>
       </x:c>
       <x:c r="E136" s="12" t="str">
         <x:v>Build a resilient and united team culture</x:v>
@@ -3834,7 +3897,7 @@
         <x:v>Developing the belief, leadership and unity needed to perform under pressure.</x:v>
       </x:c>
       <x:c r="D137" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>UTS + CI</x:v>
       </x:c>
       <x:c r="E137" s="12" t="str">
         <x:v>Build a resilient and united team culture</x:v>
@@ -3860,7 +3923,7 @@
         <x:v>Developing the belief, leadership and unity needed to perform under pressure.</x:v>
       </x:c>
       <x:c r="D138" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>UTS + CI</x:v>
       </x:c>
       <x:c r="E138" s="12" t="str">
         <x:v>Build a resilient and united team culture</x:v>
@@ -3938,7 +4001,7 @@
         <x:v>Developing the belief, leadership and unity needed to perform under pressure.</x:v>
       </x:c>
       <x:c r="D141" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>UTS + CI</x:v>
       </x:c>
       <x:c r="E141" s="12" t="str">
         <x:v>Build a resilient and united team culture</x:v>
@@ -3990,7 +4053,7 @@
         <x:v>Developing the belief, leadership and unity needed to perform under pressure.</x:v>
       </x:c>
       <x:c r="D143" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>UTS + CI</x:v>
       </x:c>
       <x:c r="E143" s="12" t="str">
         <x:v>Build a resilient and united team culture</x:v>
@@ -4016,7 +4079,7 @@
         <x:v>Developing the belief, leadership and unity needed to perform under pressure.</x:v>
       </x:c>
       <x:c r="D144" s="12" t="str">
-        <x:v>FDS</x:v>
+        <x:v>UTS + CI</x:v>
       </x:c>
       <x:c r="E144" s="12" t="str">
         <x:v>Build a resilient and united team culture</x:v>
@@ -4042,7 +4105,7 @@
         <x:v>Developing the belief, leadership and unity needed to perform under pressure.</x:v>
       </x:c>
       <x:c r="D145" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>UTS + CI</x:v>
       </x:c>
       <x:c r="E145" s="12" t="str">
         <x:v>Build a resilient and united team culture</x:v>
@@ -4068,7 +4131,7 @@
         <x:v>Using data, scouting and analysis to prepare for opponents and make better decisions.</x:v>
       </x:c>
       <x:c r="D146" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E146" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -4094,7 +4157,7 @@
         <x:v>Using data, scouting and analysis to prepare for opponents and make better decisions.</x:v>
       </x:c>
       <x:c r="D147" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E147" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -4172,7 +4235,7 @@
         <x:v>Using data, scouting and analysis to prepare for opponents and make better decisions.</x:v>
       </x:c>
       <x:c r="D150" s="12" t="str">
-        <x:v>FDS</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E150" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -4198,7 +4261,7 @@
         <x:v>Using data, scouting and analysis to prepare for opponents and make better decisions.</x:v>
       </x:c>
       <x:c r="D151" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E151" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -4250,7 +4313,7 @@
         <x:v>Using data, scouting and analysis to prepare for opponents and make better decisions.</x:v>
       </x:c>
       <x:c r="D153" s="12" t="str">
-        <x:v>UTS + CI</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E153" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -4302,7 +4365,7 @@
         <x:v>Using data, scouting and analysis to prepare for opponents and make better decisions.</x:v>
       </x:c>
       <x:c r="D155" s="12" t="str">
-        <x:v>UTS + CI</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E155" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -4328,7 +4391,7 @@
         <x:v>Using data, scouting and analysis to prepare for opponents and make better decisions.</x:v>
       </x:c>
       <x:c r="D156" s="12" t="str">
-        <x:v>FDS</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E156" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -4354,7 +4417,7 @@
         <x:v>Using data, scouting and analysis to prepare for opponents and make better decisions.</x:v>
       </x:c>
       <x:c r="D157" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E157" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -4380,7 +4443,7 @@
         <x:v>Using data, scouting and analysis to prepare for opponents and make better decisions.</x:v>
       </x:c>
       <x:c r="D158" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E158" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -4432,7 +4495,7 @@
         <x:v>Using data, scouting and analysis to prepare for opponents and make better decisions.</x:v>
       </x:c>
       <x:c r="D160" s="12" t="str">
-        <x:v>UTS + CI</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E160" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -4458,7 +4521,7 @@
         <x:v>Using data, scouting and analysis to prepare for opponents and make better decisions.</x:v>
       </x:c>
       <x:c r="D161" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E161" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -4484,7 +4547,7 @@
         <x:v>Using data, scouting and analysis to prepare for opponents and make better decisions.</x:v>
       </x:c>
       <x:c r="D162" s="12" t="str">
-        <x:v>UTS + CI + FDS</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E162" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -4510,7 +4573,7 @@
         <x:v>Using data, scouting and analysis to prepare for opponents and make better decisions.</x:v>
       </x:c>
       <x:c r="D163" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E163" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -4536,7 +4599,7 @@
         <x:v>Using data, scouting and analysis to prepare for opponents and make better decisions.</x:v>
       </x:c>
       <x:c r="D164" s="12" t="str">
-        <x:v>UTS + CI + FDS</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E164" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -4562,7 +4625,7 @@
         <x:v>Using data, scouting and analysis to prepare for opponents and make better decisions.</x:v>
       </x:c>
       <x:c r="D165" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E165" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -4588,7 +4651,7 @@
         <x:v>Using data, scouting and analysis to prepare for opponents and make better decisions.</x:v>
       </x:c>
       <x:c r="D166" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E166" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -4614,7 +4677,7 @@
         <x:v>Using data, scouting and analysis to prepare for opponents and make better decisions.</x:v>
       </x:c>
       <x:c r="D167" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E167" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -4640,7 +4703,7 @@
         <x:v>Using data, scouting and analysis to prepare for opponents and make better decisions.</x:v>
       </x:c>
       <x:c r="D168" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E168" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -4666,7 +4729,7 @@
         <x:v>Using data, scouting and analysis to prepare for opponents and make better decisions.</x:v>
       </x:c>
       <x:c r="D169" s="12" t="str">
-        <x:v>UTS + CI + FDS</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E169" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -4692,7 +4755,7 @@
         <x:v>Using data, scouting and analysis to prepare for opponents and make better decisions.</x:v>
       </x:c>
       <x:c r="D170" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E170" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -4718,7 +4781,7 @@
         <x:v>Using data, scouting and analysis to prepare for opponents and make better decisions.</x:v>
       </x:c>
       <x:c r="D171" s="12" t="str">
-        <x:v>UTS + CI</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E171" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -4770,7 +4833,7 @@
         <x:v>Using data, scouting and analysis to prepare for opponents and make better decisions.</x:v>
       </x:c>
       <x:c r="D173" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E173" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -4796,7 +4859,7 @@
         <x:v>Turning corners, free kicks, penalties and small details into decisive tournament advantages.</x:v>
       </x:c>
       <x:c r="D174" s="12" t="str">
-        <x:v>UTS + CI</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E174" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -4822,7 +4885,7 @@
         <x:v>Turning corners, free kicks, penalties and small details into decisive tournament advantages.</x:v>
       </x:c>
       <x:c r="D175" s="12" t="str">
-        <x:v>UTS + CI</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E175" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -4874,7 +4937,7 @@
         <x:v>Turning corners, free kicks, penalties and small details into decisive tournament advantages.</x:v>
       </x:c>
       <x:c r="D177" s="12" t="str">
-        <x:v>UTS + CI</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E177" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -4926,7 +4989,7 @@
         <x:v>Turning corners, free kicks, penalties and small details into decisive tournament advantages.</x:v>
       </x:c>
       <x:c r="D179" s="12" t="str">
-        <x:v>FDS</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E179" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -4978,7 +5041,7 @@
         <x:v>Turning corners, free kicks, penalties and small details into decisive tournament advantages.</x:v>
       </x:c>
       <x:c r="D181" s="12" t="str">
-        <x:v>UTS + CI + FDS</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E181" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -5004,7 +5067,7 @@
         <x:v>Turning corners, free kicks, penalties and small details into decisive tournament advantages.</x:v>
       </x:c>
       <x:c r="D182" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E182" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -5030,7 +5093,7 @@
         <x:v>Turning corners, free kicks, penalties and small details into decisive tournament advantages.</x:v>
       </x:c>
       <x:c r="D183" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E183" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -5056,7 +5119,7 @@
         <x:v>Turning corners, free kicks, penalties and small details into decisive tournament advantages.</x:v>
       </x:c>
       <x:c r="D184" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E184" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -5082,7 +5145,7 @@
         <x:v>Turning corners, free kicks, penalties and small details into decisive tournament advantages.</x:v>
       </x:c>
       <x:c r="D185" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E185" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -5108,7 +5171,7 @@
         <x:v>Turning corners, free kicks, penalties and small details into decisive tournament advantages.</x:v>
       </x:c>
       <x:c r="D186" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E186" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -5160,7 +5223,7 @@
         <x:v>Turning corners, free kicks, penalties and small details into decisive tournament advantages.</x:v>
       </x:c>
       <x:c r="D188" s="12" t="str">
-        <x:v>UTS + CI + FDS</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E188" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -5186,7 +5249,7 @@
         <x:v>Turning corners, free kicks, penalties and small details into decisive tournament advantages.</x:v>
       </x:c>
       <x:c r="D189" s="12" t="str">
-        <x:v>FDS</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E189" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -5212,7 +5275,7 @@
         <x:v>Turning corners, free kicks, penalties and small details into decisive tournament advantages.</x:v>
       </x:c>
       <x:c r="D190" s="12" t="str">
-        <x:v>UTS + CI + FDS</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E190" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -5238,7 +5301,7 @@
         <x:v>Turning corners, free kicks, penalties and small details into decisive tournament advantages.</x:v>
       </x:c>
       <x:c r="D191" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E191" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -5264,7 +5327,7 @@
         <x:v>Turning corners, free kicks, penalties and small details into decisive tournament advantages.</x:v>
       </x:c>
       <x:c r="D192" s="12" t="str">
-        <x:v>FDS</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E192" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -5290,7 +5353,7 @@
         <x:v>Turning corners, free kicks, penalties and small details into decisive tournament advantages.</x:v>
       </x:c>
       <x:c r="D193" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E193" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -5316,7 +5379,7 @@
         <x:v>Turning corners, free kicks, penalties and small details into decisive tournament advantages.</x:v>
       </x:c>
       <x:c r="D194" s="12" t="str">
-        <x:v>FDS</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E194" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -5342,7 +5405,7 @@
         <x:v>Turning corners, free kicks, penalties and small details into decisive tournament advantages.</x:v>
       </x:c>
       <x:c r="D195" s="12" t="str">
-        <x:v>UTS + CI</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E195" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -5368,7 +5431,7 @@
         <x:v>Turning corners, free kicks, penalties and small details into decisive tournament advantages.</x:v>
       </x:c>
       <x:c r="D196" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E196" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -5394,7 +5457,7 @@
         <x:v>Turning corners, free kicks, penalties and small details into decisive tournament advantages.</x:v>
       </x:c>
       <x:c r="D197" s="12" t="str">
-        <x:v>UTS + CI</x:v>
+        <x:v>UTS + FDS</x:v>
       </x:c>
       <x:c r="E197" s="12" t="str">
         <x:v>Win matches through intelligence and preparation</x:v>
@@ -5420,7 +5483,7 @@
         <x:v>Developing future players and national systems that sustain success beyond one tournament.</x:v>
       </x:c>
       <x:c r="D198" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E198" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -5498,7 +5561,7 @@
         <x:v>Developing future players and national systems that sustain success beyond one tournament.</x:v>
       </x:c>
       <x:c r="D201" s="12" t="str">
-        <x:v>FDS</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E201" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -5524,7 +5587,7 @@
         <x:v>Developing future players and national systems that sustain success beyond one tournament.</x:v>
       </x:c>
       <x:c r="D202" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E202" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -5550,7 +5613,7 @@
         <x:v>Developing future players and national systems that sustain success beyond one tournament.</x:v>
       </x:c>
       <x:c r="D203" s="12" t="str">
-        <x:v>UTS + CI + FDS</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E203" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -5576,7 +5639,7 @@
         <x:v>Developing future players and national systems that sustain success beyond one tournament.</x:v>
       </x:c>
       <x:c r="D204" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E204" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -5602,7 +5665,7 @@
         <x:v>Developing future players and national systems that sustain success beyond one tournament.</x:v>
       </x:c>
       <x:c r="D205" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E205" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -5628,7 +5691,7 @@
         <x:v>Developing future players and national systems that sustain success beyond one tournament.</x:v>
       </x:c>
       <x:c r="D206" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E206" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -5654,7 +5717,7 @@
         <x:v>Developing future players and national systems that sustain success beyond one tournament.</x:v>
       </x:c>
       <x:c r="D207" s="12" t="str">
-        <x:v>UTS + CI + FDS</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E207" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -5706,7 +5769,7 @@
         <x:v>Developing future players and national systems that sustain success beyond one tournament.</x:v>
       </x:c>
       <x:c r="D209" s="12" t="str">
-        <x:v>FDS</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E209" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -5732,7 +5795,7 @@
         <x:v>Developing future players and national systems that sustain success beyond one tournament.</x:v>
       </x:c>
       <x:c r="D210" s="12" t="str">
-        <x:v>UTS + CI + FDS</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E210" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -5784,7 +5847,7 @@
         <x:v>Developing future players and national systems that sustain success beyond one tournament.</x:v>
       </x:c>
       <x:c r="D212" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E212" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -5810,7 +5873,7 @@
         <x:v>Developing future players and national systems that sustain success beyond one tournament.</x:v>
       </x:c>
       <x:c r="D213" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E213" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -5836,7 +5899,7 @@
         <x:v>Developing future players and national systems that sustain success beyond one tournament.</x:v>
       </x:c>
       <x:c r="D214" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E214" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -5862,7 +5925,7 @@
         <x:v>Developing future players and national systems that sustain success beyond one tournament.</x:v>
       </x:c>
       <x:c r="D215" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E215" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -5888,7 +5951,7 @@
         <x:v>Developing future players and national systems that sustain success beyond one tournament.</x:v>
       </x:c>
       <x:c r="D216" s="12" t="str">
-        <x:v>FDS</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E216" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -5914,7 +5977,7 @@
         <x:v>Developing future players and national systems that sustain success beyond one tournament.</x:v>
       </x:c>
       <x:c r="D217" s="12" t="str">
-        <x:v>UTS + CI + FDS</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E217" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -5940,7 +6003,7 @@
         <x:v>Developing future players and national systems that sustain success beyond one tournament.</x:v>
       </x:c>
       <x:c r="D218" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E218" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -5966,7 +6029,7 @@
         <x:v>Developing future players and national systems that sustain success beyond one tournament.</x:v>
       </x:c>
       <x:c r="D219" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E219" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -5992,7 +6055,7 @@
         <x:v>Developing future players and national systems that sustain success beyond one tournament.</x:v>
       </x:c>
       <x:c r="D220" s="12" t="str">
-        <x:v>UTS + CI + FDS</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E220" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -6018,7 +6081,7 @@
         <x:v>Developing future players and national systems that sustain success beyond one tournament.</x:v>
       </x:c>
       <x:c r="D221" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E221" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -6044,7 +6107,7 @@
         <x:v>Building trust, public support and a strong national story around the team.</x:v>
       </x:c>
       <x:c r="D222" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>UTS + CI + FDS</x:v>
       </x:c>
       <x:c r="E222" s="12" t="str">
         <x:v>Strengthen national belief and external support</x:v>
@@ -6070,7 +6133,7 @@
         <x:v>Building trust, public support and a strong national story around the team.</x:v>
       </x:c>
       <x:c r="D223" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>UTS + CI + FDS</x:v>
       </x:c>
       <x:c r="E223" s="12" t="str">
         <x:v>Strengthen national belief and external support</x:v>
@@ -6096,7 +6159,7 @@
         <x:v>Building trust, public support and a strong national story around the team.</x:v>
       </x:c>
       <x:c r="D224" s="12" t="str">
-        <x:v>FDS</x:v>
+        <x:v>UTS + CI + FDS</x:v>
       </x:c>
       <x:c r="E224" s="12" t="str">
         <x:v>Strengthen national belief and external support</x:v>
@@ -6122,7 +6185,7 @@
         <x:v>Building trust, public support and a strong national story around the team.</x:v>
       </x:c>
       <x:c r="D225" s="12" t="str">
-        <x:v>UTS + CI</x:v>
+        <x:v>UTS + CI + FDS</x:v>
       </x:c>
       <x:c r="E225" s="12" t="str">
         <x:v>Strengthen national belief and external support</x:v>
@@ -6148,7 +6211,7 @@
         <x:v>Building trust, public support and a strong national story around the team.</x:v>
       </x:c>
       <x:c r="D226" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>UTS + CI + FDS</x:v>
       </x:c>
       <x:c r="E226" s="12" t="str">
         <x:v>Strengthen national belief and external support</x:v>
@@ -6174,7 +6237,7 @@
         <x:v>Building trust, public support and a strong national story around the team.</x:v>
       </x:c>
       <x:c r="D227" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>UTS + CI + FDS</x:v>
       </x:c>
       <x:c r="E227" s="12" t="str">
         <x:v>Strengthen national belief and external support</x:v>
@@ -6200,7 +6263,7 @@
         <x:v>Building trust, public support and a strong national story around the team.</x:v>
       </x:c>
       <x:c r="D228" s="12" t="str">
-        <x:v>FDS</x:v>
+        <x:v>UTS + CI + FDS</x:v>
       </x:c>
       <x:c r="E228" s="12" t="str">
         <x:v>Strengthen national belief and external support</x:v>
@@ -6278,7 +6341,7 @@
         <x:v>Building trust, public support and a strong national story around the team.</x:v>
       </x:c>
       <x:c r="D231" s="12" t="str">
-        <x:v>FDS</x:v>
+        <x:v>UTS + CI + FDS</x:v>
       </x:c>
       <x:c r="E231" s="12" t="str">
         <x:v>Strengthen national belief and external support</x:v>
@@ -6304,7 +6367,7 @@
         <x:v>Building trust, public support and a strong national story around the team.</x:v>
       </x:c>
       <x:c r="D232" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>UTS + CI + FDS</x:v>
       </x:c>
       <x:c r="E232" s="12" t="str">
         <x:v>Strengthen national belief and external support</x:v>
@@ -6330,7 +6393,7 @@
         <x:v>Building trust, public support and a strong national story around the team.</x:v>
       </x:c>
       <x:c r="D233" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>UTS + CI + FDS</x:v>
       </x:c>
       <x:c r="E233" s="12" t="str">
         <x:v>Strengthen national belief and external support</x:v>
@@ -6356,7 +6419,7 @@
         <x:v>Building trust, public support and a strong national story around the team.</x:v>
       </x:c>
       <x:c r="D234" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>UTS + CI + FDS</x:v>
       </x:c>
       <x:c r="E234" s="12" t="str">
         <x:v>Strengthen national belief and external support</x:v>
@@ -6382,7 +6445,7 @@
         <x:v>Building trust, public support and a strong national story around the team.</x:v>
       </x:c>
       <x:c r="D235" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>UTS + CI + FDS</x:v>
       </x:c>
       <x:c r="E235" s="12" t="str">
         <x:v>Strengthen national belief and external support</x:v>
@@ -6408,7 +6471,7 @@
         <x:v>Building trust, public support and a strong national story around the team.</x:v>
       </x:c>
       <x:c r="D236" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>UTS + CI + FDS</x:v>
       </x:c>
       <x:c r="E236" s="12" t="str">
         <x:v>Strengthen national belief and external support</x:v>
@@ -6434,7 +6497,7 @@
         <x:v>Building trust, public support and a strong national story around the team.</x:v>
       </x:c>
       <x:c r="D237" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>UTS + CI + FDS</x:v>
       </x:c>
       <x:c r="E237" s="12" t="str">
         <x:v>Strengthen national belief and external support</x:v>
@@ -6460,7 +6523,7 @@
         <x:v>Building trust, public support and a strong national story around the team.</x:v>
       </x:c>
       <x:c r="D238" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>UTS + CI + FDS</x:v>
       </x:c>
       <x:c r="E238" s="12" t="str">
         <x:v>Strengthen national belief and external support</x:v>
@@ -6486,7 +6549,7 @@
         <x:v>Building trust, public support and a strong national story around the team.</x:v>
       </x:c>
       <x:c r="D239" s="12" t="str">
-        <x:v>UTS + CI</x:v>
+        <x:v>UTS + CI + FDS</x:v>
       </x:c>
       <x:c r="E239" s="12" t="str">
         <x:v>Strengthen national belief and external support</x:v>
@@ -6538,7 +6601,7 @@
         <x:v>Building trust, public support and a strong national story around the team.</x:v>
       </x:c>
       <x:c r="D241" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>UTS + CI + FDS</x:v>
       </x:c>
       <x:c r="E241" s="12" t="str">
         <x:v>Strengthen national belief and external support</x:v>
@@ -6590,7 +6653,7 @@
         <x:v>Building trust, public support and a strong national story around the team.</x:v>
       </x:c>
       <x:c r="D243" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>UTS + CI + FDS</x:v>
       </x:c>
       <x:c r="E243" s="12" t="str">
         <x:v>Strengthen national belief and external support</x:v>
@@ -6642,7 +6705,7 @@
         <x:v>Building trust, public support and a strong national story around the team.</x:v>
       </x:c>
       <x:c r="D245" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>UTS + CI + FDS</x:v>
       </x:c>
       <x:c r="E245" s="12" t="str">
         <x:v>Strengthen national belief and external support</x:v>
@@ -6668,7 +6731,7 @@
         <x:v>Ensuring preparation, travel, accommodation and operations support peak performance.</x:v>
       </x:c>
       <x:c r="D246" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E246" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -6694,7 +6757,7 @@
         <x:v>Ensuring preparation, travel, accommodation and operations support peak performance.</x:v>
       </x:c>
       <x:c r="D247" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E247" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -6720,7 +6783,7 @@
         <x:v>Ensuring preparation, travel, accommodation and operations support peak performance.</x:v>
       </x:c>
       <x:c r="D248" s="12" t="str">
-        <x:v>UTS + CI</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E248" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -6746,7 +6809,7 @@
         <x:v>Ensuring preparation, travel, accommodation and operations support peak performance.</x:v>
       </x:c>
       <x:c r="D249" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E249" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -6772,7 +6835,7 @@
         <x:v>Ensuring preparation, travel, accommodation and operations support peak performance.</x:v>
       </x:c>
       <x:c r="D250" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E250" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -6824,7 +6887,7 @@
         <x:v>Ensuring preparation, travel, accommodation and operations support peak performance.</x:v>
       </x:c>
       <x:c r="D252" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E252" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -6850,7 +6913,7 @@
         <x:v>Ensuring preparation, travel, accommodation and operations support peak performance.</x:v>
       </x:c>
       <x:c r="D253" s="12" t="str">
-        <x:v>UTS + CI + FDS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E253" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -6876,7 +6939,7 @@
         <x:v>Ensuring preparation, travel, accommodation and operations support peak performance.</x:v>
       </x:c>
       <x:c r="D254" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E254" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -6902,7 +6965,7 @@
         <x:v>Ensuring preparation, travel, accommodation and operations support peak performance.</x:v>
       </x:c>
       <x:c r="D255" s="12" t="str">
-        <x:v>UTS + CI</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E255" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -6928,7 +6991,7 @@
         <x:v>Ensuring preparation, travel, accommodation and operations support peak performance.</x:v>
       </x:c>
       <x:c r="D256" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E256" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -6954,7 +7017,7 @@
         <x:v>Ensuring preparation, travel, accommodation and operations support peak performance.</x:v>
       </x:c>
       <x:c r="D257" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E257" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -6980,7 +7043,7 @@
         <x:v>Ensuring preparation, travel, accommodation and operations support peak performance.</x:v>
       </x:c>
       <x:c r="D258" s="12" t="str">
-        <x:v>UTS + CI + FDS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E258" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -7006,7 +7069,7 @@
         <x:v>Ensuring preparation, travel, accommodation and operations support peak performance.</x:v>
       </x:c>
       <x:c r="D259" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E259" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -7032,7 +7095,7 @@
         <x:v>Ensuring preparation, travel, accommodation and operations support peak performance.</x:v>
       </x:c>
       <x:c r="D260" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E260" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -7058,7 +7121,7 @@
         <x:v>Ensuring preparation, travel, accommodation and operations support peak performance.</x:v>
       </x:c>
       <x:c r="D261" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E261" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -7084,7 +7147,7 @@
         <x:v>Ensuring preparation, travel, accommodation and operations support peak performance.</x:v>
       </x:c>
       <x:c r="D262" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E262" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -7136,7 +7199,7 @@
         <x:v>Ensuring preparation, travel, accommodation and operations support peak performance.</x:v>
       </x:c>
       <x:c r="D264" s="12" t="str">
-        <x:v>UTS + CI</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E264" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -7162,7 +7225,7 @@
         <x:v>Ensuring preparation, travel, accommodation and operations support peak performance.</x:v>
       </x:c>
       <x:c r="D265" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E265" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -7188,7 +7251,7 @@
         <x:v>Ensuring preparation, travel, accommodation and operations support peak performance.</x:v>
       </x:c>
       <x:c r="D266" s="12" t="str">
-        <x:v>CI + FDS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E266" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -7240,7 +7303,7 @@
         <x:v>Ensuring preparation, travel, accommodation and operations support peak performance.</x:v>
       </x:c>
       <x:c r="D268" s="12" t="str">
-        <x:v>UTS + CI</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E268" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -7266,7 +7329,7 @@
         <x:v>Ensuring preparation, travel, accommodation and operations support peak performance.</x:v>
       </x:c>
       <x:c r="D269" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>FDS</x:v>
       </x:c>
       <x:c r="E269" s="12" t="str">
         <x:v>Prepare players to perform across the full tournament</x:v>
@@ -7292,7 +7355,7 @@
         <x:v>Strengthening the coaching team, support staff and learning systems behind the squad.</x:v>
       </x:c>
       <x:c r="D270" s="12" t="str">
-        <x:v>UTS + CI</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E270" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -7318,7 +7381,7 @@
         <x:v>Strengthening the coaching team, support staff and learning systems behind the squad.</x:v>
       </x:c>
       <x:c r="D271" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E271" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -7344,7 +7407,7 @@
         <x:v>Strengthening the coaching team, support staff and learning systems behind the squad.</x:v>
       </x:c>
       <x:c r="D272" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E272" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -7370,7 +7433,7 @@
         <x:v>Strengthening the coaching team, support staff and learning systems behind the squad.</x:v>
       </x:c>
       <x:c r="D273" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E273" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -7396,7 +7459,7 @@
         <x:v>Strengthening the coaching team, support staff and learning systems behind the squad.</x:v>
       </x:c>
       <x:c r="D274" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E274" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -7422,7 +7485,7 @@
         <x:v>Strengthening the coaching team, support staff and learning systems behind the squad.</x:v>
       </x:c>
       <x:c r="D275" s="12" t="str">
-        <x:v>FDS</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E275" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -7448,7 +7511,7 @@
         <x:v>Strengthening the coaching team, support staff and learning systems behind the squad.</x:v>
       </x:c>
       <x:c r="D276" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E276" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -7474,7 +7537,7 @@
         <x:v>Strengthening the coaching team, support staff and learning systems behind the squad.</x:v>
       </x:c>
       <x:c r="D277" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E277" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -7500,7 +7563,7 @@
         <x:v>Strengthening the coaching team, support staff and learning systems behind the squad.</x:v>
       </x:c>
       <x:c r="D278" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E278" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -7526,7 +7589,7 @@
         <x:v>Strengthening the coaching team, support staff and learning systems behind the squad.</x:v>
       </x:c>
       <x:c r="D279" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E279" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -7552,7 +7615,7 @@
         <x:v>Strengthening the coaching team, support staff and learning systems behind the squad.</x:v>
       </x:c>
       <x:c r="D280" s="12" t="str">
-        <x:v>UTS + FDS</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E280" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -7578,7 +7641,7 @@
         <x:v>Strengthening the coaching team, support staff and learning systems behind the squad.</x:v>
       </x:c>
       <x:c r="D281" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E281" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -7604,7 +7667,7 @@
         <x:v>Strengthening the coaching team, support staff and learning systems behind the squad.</x:v>
       </x:c>
       <x:c r="D282" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E282" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -7630,7 +7693,7 @@
         <x:v>Strengthening the coaching team, support staff and learning systems behind the squad.</x:v>
       </x:c>
       <x:c r="D283" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E283" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -7708,7 +7771,7 @@
         <x:v>Strengthening the coaching team, support staff and learning systems behind the squad.</x:v>
       </x:c>
       <x:c r="D286" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E286" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -7734,7 +7797,7 @@
         <x:v>Strengthening the coaching team, support staff and learning systems behind the squad.</x:v>
       </x:c>
       <x:c r="D287" s="12" t="str">
-        <x:v>CI</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E287" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -7760,7 +7823,7 @@
         <x:v>Strengthening the coaching team, support staff and learning systems behind the squad.</x:v>
       </x:c>
       <x:c r="D288" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E288" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -7786,7 +7849,7 @@
         <x:v>Strengthening the coaching team, support staff and learning systems behind the squad.</x:v>
       </x:c>
       <x:c r="D289" s="12" t="str">
-        <x:v>UTS</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E289" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -7812,7 +7875,7 @@
         <x:v>Strengthening the coaching team, support staff and learning systems behind the squad.</x:v>
       </x:c>
       <x:c r="D290" s="12" t="str">
-        <x:v>UTS + CI + FDS</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E290" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -7838,7 +7901,7 @@
         <x:v>Strengthening the coaching team, support staff and learning systems behind the squad.</x:v>
       </x:c>
       <x:c r="D291" s="12" t="str">
-        <x:v>FDS</x:v>
+        <x:v>CI + FDS</x:v>
       </x:c>
       <x:c r="E291" s="12" t="str">
         <x:v>Sustain success beyond one tournament</x:v>
@@ -7864,7 +7927,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6c019ab3e6443dc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a9302b3a0ee4c09"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7930,13 +7993,13 @@
         <x:v>Venn zones</x:v>
       </x:c>
       <x:c r="B7" t="str">
-        <x:v>Randomly assigned using UTS / CI / FDS combinations</x:v>
+        <x:v>Randomised consistently by objective so ideas, themes and objectives sit across different Venn zones</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5cf2206ac25344db"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f089fe2507c4831"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8074,7 +8137,159 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb6d6b20db9740cb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe1f63419d374e3d"/>
   </x:tableParts>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="11.25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="11.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="10.5" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="6.5" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="8.5" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="19" t="str">
+        <x:v>Venn Zone</x:v>
+      </x:c>
+      <x:c r="B1" s="19" t="str">
+        <x:v>Mapped Rows</x:v>
+      </x:c>
+      <x:c r="C1" s="19" t="str">
+        <x:v>Unique Ideas</x:v>
+      </x:c>
+      <x:c r="D1" s="19" t="str">
+        <x:v>Themes</x:v>
+      </x:c>
+      <x:c r="E1" s="19" t="str">
+        <x:v>Objectives</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="20" t="str">
+        <x:v>UTS</x:v>
+      </x:c>
+      <x:c r="B2" s="21" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C2" s="21" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D2" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E2" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="23" t="str">
+        <x:v>CI</x:v>
+      </x:c>
+      <x:c r="B3" s="24" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C3" s="24" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D3" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E3" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="23" t="str">
+        <x:v>FDS</x:v>
+      </x:c>
+      <x:c r="B4" s="24" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C4" s="24" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D4" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E4" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="23" t="str">
+        <x:v>UTS + CI</x:v>
+      </x:c>
+      <x:c r="B5" s="24" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C5" s="24" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D5" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E5" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="23" t="str">
+        <x:v>UTS + FDS</x:v>
+      </x:c>
+      <x:c r="B6" s="24" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C6" s="24" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D6" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E6" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="23" t="str">
+        <x:v>CI + FDS</x:v>
+      </x:c>
+      <x:c r="B7" s="24" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C7" s="24" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D7" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E7" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="26" t="str">
+        <x:v>UTS + CI + FDS</x:v>
+      </x:c>
+      <x:c r="B8" s="27" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C8" s="27" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D8" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E8" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>